--- a/ProductBacklog-Nhom20.xlsx
+++ b/ProductBacklog-Nhom20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\My doc IT\CNPMNC\ly thuyet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1098A0F1-E1A9-4B46-965C-101D9F93F178}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82690F1-4812-426F-BF70-EB5096481C47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1399,7 +1399,9 @@
       <c r="E4" s="15">
         <v>45912</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="15">
+        <v>45961</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
@@ -1417,7 +1419,9 @@
       <c r="E5" s="15">
         <v>45912</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="15">
+        <v>45961</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
@@ -1435,7 +1439,9 @@
       <c r="E6" s="15">
         <v>45912</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="15">
+        <v>45961</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
@@ -1453,7 +1459,9 @@
       <c r="E7" s="15">
         <v>45912</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="15">
+        <v>45961</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
@@ -1471,7 +1479,9 @@
       <c r="E8" s="15">
         <v>45912</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="15">
+        <v>45961</v>
+      </c>
     </row>
     <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
